--- a/DATA/demand/antigen_demand_80_20_5_scenarios.xlsx
+++ b/DATA/demand/antigen_demand_80_20_5_scenarios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,11 +476,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[721305600, 607877300, 764516000, 982491000, 987422300, 757674000, 1035638100, 1237728200, 1546474500, 1814942600]</t>
+          <t>[690293000, 540644300, 663354000, 1033467400, 832363600, 964285900, 1484889200, 781961600, 1006661500, 199939900]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05840000000000001</v>
+        <v>0.0188</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -494,11 +494,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[647378800, 742510700, 689045800, 881044300, 822821100, 1281798700, 1128053500, 1593513600, 1901076600, 2209600200]</t>
+          <t>[654233900, 836474800, 765804800, 925613800, 851169600, 917181600, 1346325300, 1152974500, 669109400, -2147483648]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.06320000000000002</v>
+        <v>0.08240000000000003</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -512,11 +512,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[628683100, 902179600, 930527900, 784884400, 948846900, 968245400, 1197406100, 1685927300, 1715922200, 804875700]</t>
+          <t>[596906900, 558336500, 812533400, 660834400, 686912400, 1059413800, 1410783900, 1252908300, 953910300, 1577938400]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04800000000000002</v>
+        <v>0.07720000000000003</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -530,11 +530,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[701162500, 752136300, 770118000, 924806500, 1036967400, 1059736600, 1142626600, 1201632600, 661981200, 2816464600]</t>
+          <t>[743387800, 718494700, 836301100, 720152500, 761304900, 1033130400, 1046414400, 1046244900, -2147483648, 1368714300]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03040000000000001</v>
+        <v>0.0216</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -566,11 +566,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[29084800, 32704300, 40347600, 46291700, 51390100, 58763900, 65250000, 75108800, 81309300, 90655800]</t>
+          <t>[27408100, 36795300, 44960900, 42153100, 54014700, 57247900, 67205500, 74837800, 78713600, 88601800]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.07160000000000002</v>
+        <v>0.03400000000000001</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -584,11 +584,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[29816400, 33915000, 42553200, 45772400, 54775100, 56551100, 72566600, 70849100, 81312000, 82426500]</t>
+          <t>[29278100, 34529800, 41314600, 46831600, 52100600, 61799200, 68661300, 71927100, 88594400, 94993400]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.04880000000000002</v>
+        <v>0.06360000000000002</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[30047000, 35880400, 40015900, 48665400, 52933300, 61583100, 61330100, 71828400, 71158400, 97715100]</t>
+          <t>[26509800, 35593800, 41761900, 46914800, 51357500, 59171600, 66488200, 73483500, 84634900, 80794100]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03560000000000001</v>
+        <v>0.06240000000000001</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -620,11 +620,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[28333300, 37169000, 41218500, 47636600, 57445600, 60264600, 67950700, 77239200, 74056200, 82736400]</t>
+          <t>[26621500, 38049900, 42725200, 46993500, 54230900, 60065400, 65293500, 74388900, 68226900, 92640900]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.04400000000000002</v>
+        <v>0.04000000000000001</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -656,11 +656,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[377042200, 391292300, 444910100, 366676900, 430917600, 471673600, 396718600, 415360200, 429893100, 396961400]</t>
+          <t>[410703700, 394726600, 455058800, 440667600, 324876000, 458683900, 473285200, 433237300, 448206300, 436645900]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.07040000000000002</v>
+        <v>0.05000000000000002</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -674,11 +674,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[429510600, 414860400, 332028200, 406042400, 415981600, 325713600, 306477700, 425822300, 387285700, 539674500]</t>
+          <t>[367899800, 397096100, 371863600, 396265400, 481334800, 460819700, 394718400, 307416400, 352012500, 467247100]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.05680000000000001</v>
+        <v>0.06600000000000002</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -692,11 +692,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[386370700, 349680200, 476757100, 389432900, 422597800, 377179700, 453970400, 519669800, 576826900, 416957000]</t>
+          <t>[398538000, 411746900, 404101000, 294154800, 354466900, 365673200, 370291900, 345678000, 544177700, 350602700]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.04400000000000002</v>
+        <v>0.04560000000000002</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -710,11 +710,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[446414800, 430021100, 394503300, 361562200, 365081000, 415087600, 538352200, 218673800, 299858600, 299182300]</t>
+          <t>[358192200, 354219100, 361021300, 411500900, 475530300, 470809100, 452294400, 416526500, 568066500, 503505000]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02880000000000001</v>
+        <v>0.03840000000000002</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[308286600, 315190100, 306568100, 360161400, 325621200, 349473100, 373814800, 410076400, 380680400, 400860200]</t>
+          <t>[308462400, 308564000, 317849200, 348113400, 353835500, 364190100, 361704000, 387351100, 363068900, 408753500]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.06320000000000002</v>
+        <v>0.06600000000000002</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -764,11 +764,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[282097000, 294951100, 307037800, 345568200, 385154800, 356661700, 335398200, 346463200, 389063800, 386288100]</t>
+          <t>[296797500, 286435900, 324747800, 327110000, 358279900, 386356000, 373120300, 367969400, 422523900, 380845900]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.04680000000000002</v>
+        <v>0.05040000000000003</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -782,11 +782,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[303338100, 300029300, 309171200, 325121100, 374328300, 351655500, 362442400, 425451400, 412953800, 449355900]</t>
+          <t>[290485200, 340862100, 301672100, 347190200, 369051400, 309998000, 379238500, 385344800, 435675100, 417032400]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.05360000000000001</v>
+        <v>0.04560000000000002</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -800,11 +800,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[312698100, 330036000, 315317400, 322869200, 319461500, 342058400, 393751700, 348094100, 417040800, 351266100]</t>
+          <t>[292457000, 315010000, 326207300, 332843200, 350062400, 362530200, 399440500, 394371600, 351868000, 351641500]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.03640000000000001</v>
+        <v>0.03800000000000001</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -813,12 +813,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IPV</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[522182000, 582182300, 608631800, 590689600, 591743500, 572503000, 130824100, 128516200, 130807300, 132956000]</t>
+          <t>[420097000, 358616900, 394831600, 346093200, 377569100, 407486200, 271512200, 386591100, 290515900, 326808200]</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -836,14 +836,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[420097000, 358616900, 394831600, 346093200, 377569100, 407486200, 271512200, 386591100, 290515900, 326808200]</t>
+          <t>[520688600, 599384600, 741765500, 584291600, 610795400, 751325700, 699010900, 831020100, 825941600, 1061105100]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.8</v>
+        <v>0.05720000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -854,14 +854,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[366119100, 543550200, 567452200, 772603400, 584439900, 529137600, 744568200, 861299600, 964707000, 1126439100]</t>
+          <t>[558200700, 568584000, 470701300, 569931600, 693752000, 880470900, 794733300, 944858600, 1111350000, 635813500]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.06160000000000002</v>
+        <v>0.06320000000000002</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -872,14 +872,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[405839100, 455568900, 681147400, 627650500, 713157900, 652165400, 1018570600, 897244600, 786260000, 483252300]</t>
+          <t>[396235400, 525423200, 507983700, 478856400, 600172200, 551044600, 684851800, 969568700, 991050500, 1391486700]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.04440000000000002</v>
+        <v>0.04520000000000002</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -890,32 +890,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[411611500, 528165300, 631294700, 615935500, 812768700, 900786500, 774889600, 842838000, 630096900, 1242553800]</t>
+          <t>[403209300, 477992600, 574350300, 589385100, 625684300, 571410200, 1164655200, 647187900, 942801300, 1502330400]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.03440000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Mumps</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[417228900, 631721900, 392223000, 661729600, 603206600, 745085800, 598087600, 783790800, 1276545300, 562374400]</t>
+          <t>[26052200, 26626400, 25785400, 25268100, 23536200, 16205400, 18650400, 8909600, 10718500, 12977700]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -926,14 +926,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[26052200, 26626400, 25785400, 25268100, 23536200, 16205400, 18650400, 8909600, 10718500, 12977700]</t>
+          <t>[22927300, 20932900, 31158300, 29486900, 34069800, 45473700, 44507600, 44743800, 56776500, 52293200]</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.8</v>
+        <v>0.05600000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -944,14 +944,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[26434800, 24319300, 27811700, 44657200, 43736900, 46543400, 49246100, 52944000, 71912300, 67062900]</t>
+          <t>[25298900, 35825600, 28309600, 34167200, 56941500, 34282800, 52971000, 61662700, 54703300, 79141000]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.05040000000000003</v>
+        <v>0.05840000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -962,14 +962,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[28215800, 39271900, 26145900, 32142700, 37334400, 35567200, 40523000, 45905700, 22387000, 67095200]</t>
+          <t>[20805100, 27986400, 29062300, 31362300, 32914000, 34978900, 49196300, 36209300, 95135900, 77415800]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0532</v>
+        <v>0.04000000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -980,32 +980,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[23572700, 22275400, 30824600, 36527000, 29638400, 31874800, 41700300, 48868900, 82418700, 40299500]</t>
+          <t>[28568900, 44316300, 29910400, 42925000, 43035900, 34138600, 37070300, 62755300, 51887400, 32244300]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.04840000000000003</v>
+        <v>0.04560000000000002</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mumps</t>
+          <t>PCV</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[21806000, 26058500, 42128400, 38193800, 36105900, 43818000, 42625400, 59170900, 58905700, 92252200]</t>
+          <t>[160800200, 186996100, 209165500, 205938500, 220998700, 219106600, 222271100, 217335600, 218764600, 220234300]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.04800000000000002</v>
+        <v>0.8</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[160800200, 186996100, 209165500, 205938500, 220998700, 219106600, 222271100, 217335600, 218764600, 220234300]</t>
+          <t>[229980600, 255538100, 322750600, 318306500, 363296300, 369410900, 285323300, 435396500, 470226400, 530917400]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.8</v>
+        <v>0.05560000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1034,14 +1034,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[221195800, 253552900, 261247200, 324843300, 347242400, 418956200, 388845100, 459944500, 588107100, 620033700]</t>
+          <t>[217304000, 262275300, 327108600, 328942400, 372129800, 353796500, 370562100, 492289800, 466028200, 179323800]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.06480000000000001</v>
+        <v>0.04840000000000003</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -1052,14 +1052,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[218370800, 277317500, 272161800, 336877000, 303477200, 376405200, 376695800, 408727900, 389361500, 355734900]</t>
+          <t>[228025000, 270527400, 333973500, 349599500, 355922500, 316447400, 486664800, 392780800, 529487100, 752423700]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.05360000000000001</v>
+        <v>0.05040000000000003</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -1070,32 +1070,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[226540800, 269992000, 305184600, 341442300, 349236700, 379368400, 306376800, 499225000, 291243400, 704392400]</t>
+          <t>[217608200, 267216900, 253205600, 301483300, 300469200, 342484400, 447616200, 324915700, 327715900, 505043600]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.04840000000000003</v>
+        <v>0.04560000000000002</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PCV</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[236848300, 250640400, 260853400, 317766300, 362084600, 275024500, 491205600, 426762800, 661293600, 308801800]</t>
+          <t>[320662700, 347414000, 352464600, 335977000, 334855300, 328035800, 331237500, 328308900, 331462200, 334312000]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.03320000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1106,14 +1106,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[320662700, 347414000, 352464600, 335977000, 334855300, 328035800, 331237500, 328308900, 331462200, 334312000]</t>
+          <t>[330913600, 348707600, 372077900, 358905200, 359328000, 361641600, 392197100, 366714000, 428874500, 446770700]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.8</v>
+        <v>0.06200000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -1124,14 +1124,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[355653600, 362558300, 369758300, 393885100, 373491500, 419828900, 386847700, 370419000, 407083600, 397241700]</t>
+          <t>[376053500, 329574100, 385604700, 351618800, 410530100, 375193000, 363350500, 364705100, 397681100, 335678000]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.07080000000000002</v>
+        <v>0.03920000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[365264100, 352622700, 379948000, 369418000, 369275400, 387313900, 362605700, 431397100, 343086900, 311519200]</t>
+          <t>[357621300, 377952200, 350446900, 353376700, 336929700, 391426500, 366153900, 441004100, 330439000, 377938400]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.04280000000000002</v>
+        <v>0.05480000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -1160,32 +1160,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[337527900, 312055600, 372110800, 359158800, 349983300, 337556100, 360123600, 400429700, 354562300, 464608800]</t>
+          <t>[355092700, 355017700, 382913500, 346050200, 324302200, 373866000, 390207300, 358433200, 438275500, 333775300]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.05360000000000001</v>
+        <v>0.04400000000000002</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Pertussis</t>
+          <t>Polio</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[369590100, 328467100, 340351100, 345185900, 349332400, 326665100, 366650300, 370087300, 457327000, 288273600]</t>
+          <t>[522182000, 582182300, 608631800, 590689600, 591743500, 572503000, 130824100, 128516200, 130807300, 132956000]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.03280000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1196,11 +1196,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[607676400, 627716800, 676632000, 724051100, 801478300, 800020900, 765648900, 850379200, 863179800, 985648000]</t>
+          <t>[597194100, 677401000, 776170500, 676082100, 773974800, 869915700, 861400800, 863844100, 895666700, 960509500]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.08280000000000004</v>
+        <v>0.04640000000000002</v>
       </c>
       <c r="D43" t="n">
         <v>2</v>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[707137300, 646793900, 603908300, 654115100, 728496100, 792508000, 858958300, 798171200, 951661100, 637565500]</t>
+          <t>[629319000, 636390100, 756892800, 753580500, 795712200, 761560800, 823600500, 812364000, 750291200, 951616700]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.04920000000000002</v>
+        <v>0.07000000000000002</v>
       </c>
       <c r="D44" t="n">
         <v>3</v>
@@ -1232,11 +1232,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[644209200, 624042500, 731534400, 629883100, 767065000, 678422300, 879354700, 841439600, 1035115300, 1185138100]</t>
+          <t>[674623000, 620549000, 675000300, 664288500, 754280400, 831403500, 798232300, 929329300, 980424200, 648707300]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.03560000000000001</v>
+        <v>0.04200000000000002</v>
       </c>
       <c r="D45" t="n">
         <v>4</v>
@@ -1250,11 +1250,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[625553300, 597498900, 635230100, 731991900, 663374500, 726560500, 810718300, 853090200, 629981100, 847184000]</t>
+          <t>[594500300, 683925100, 716534600, 768555600, 645396200, 685236300, 734718200, 992189000, 1016570100, 1182731700]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.03240000000000001</v>
+        <v>0.04160000000000002</v>
       </c>
       <c r="D46" t="n">
         <v>5</v>
@@ -1286,11 +1286,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[169975100, 233304200, 212495900, 297773700, 395993200, 320744300, 368739200, 631081200, 597492900, 817641900]</t>
+          <t>[176924600, 219261400, 246960500, 200506000, 250245900, 309212600, 359689500, 642248900, 549276900, 702456800]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0524</v>
+        <v>0.04600000000000002</v>
       </c>
       <c r="D48" t="n">
         <v>2</v>
@@ -1304,11 +1304,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[183850400, 228936200, 245704600, 272715200, 295795300, 252508200, 396848000, 625259900, 851783900, 374633400]</t>
+          <t>[185622400, 219556000, 256011100, 228026000, 455555300, 366778100, 385080400, 482266900, 714517200, 1041382600]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.04920000000000002</v>
+        <v>0.05560000000000001</v>
       </c>
       <c r="D49" t="n">
         <v>3</v>
@@ -1322,11 +1322,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[194576200, 262867300, 214479700, 255207900, 431228300, 386688800, 316347300, 512149200, 689598600, 1164612500]</t>
+          <t>[201197500, 175155800, 196664100, 220157400, 319305100, 338422000, 450422500, 421255000, 854993100, 366912800]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.05160000000000001</v>
+        <v>0.05480000000000001</v>
       </c>
       <c r="D50" t="n">
         <v>4</v>
@@ -1340,11 +1340,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[205837200, 206197700, 326023400, 233332500, 213260300, 325345000, 482853200, 388476200, 505916900, 537775400]</t>
+          <t>[229454700, 235817300, 294116200, 205158400, 361673800, 442510100, 369726600, 502021600, 283587800, 884340400]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.04680000000000002</v>
+        <v>0.04360000000000002</v>
       </c>
       <c r="D51" t="n">
         <v>5</v>
@@ -1376,11 +1376,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>[310927200, 643065600, 426687800, 525095400, 511615200, 563013400, 715200100, 580609700, 801822400, 805754300]</t>
+          <t>[375199800, 541952100, 425153100, 568072300, 445714300, 717977700, 625043900, 769890300, 719103700, 840127000]</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.04680000000000002</v>
+        <v>0.05720000000000001</v>
       </c>
       <c r="D53" t="n">
         <v>2</v>
@@ -1394,11 +1394,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>[354665000, 489725700, 437047700, 468395300, 487454900, 467925700, 748444600, 769833300, 379864600, 758128900]</t>
+          <t>[354209400, 444952700, 440196700, 602098200, 602205300, 567084600, 437763600, 605256900, 851193600, 458658300]</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.04960000000000003</v>
+        <v>0.05160000000000001</v>
       </c>
       <c r="D54" t="n">
         <v>3</v>
@@ -1412,11 +1412,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[348856000, 444541600, 466929600, 515901300, 729419400, 521356500, 691441000, 938376600, 887426100, 594802400]</t>
+          <t>[309860900, 475793600, 289321200, 346819600, 619977400, 600887700, 656546100, 670139400, 781452000, 1090014900]</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.04960000000000003</v>
+        <v>0.05480000000000001</v>
       </c>
       <c r="D55" t="n">
         <v>4</v>
@@ -1430,11 +1430,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[309128200, 292723600, 504558200, 471737500, 636946600, 613529200, 480183200, 644329600, 739382200, 1086184400]</t>
+          <t>[390927600, 457092000, 573694500, 428027900, 569926600, 637772500, 778011200, 633986300, 266418600, 590737700]</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.03640000000000001</v>
       </c>
       <c r="D56" t="n">
         <v>5</v>
@@ -1466,11 +1466,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>[653352900, 667872100, 697401100, 683761500, 613323200, 619211000, 686459100, 684088700, 626330200, 769020500]</t>
+          <t>[629499200, 631449500, 590716800, 662222000, 654131200, 630990900, 743740500, 701074300, 765625500, 736675300]</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.05800000000000001</v>
+        <v>0.06080000000000001</v>
       </c>
       <c r="D58" t="n">
         <v>2</v>
@@ -1484,11 +1484,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[659194300, 635964000, 652638500, 739784300, 643542100, 702212400, 681381000, 734002400, 772251000, 598333500]</t>
+          <t>[649813800, 621341400, 724413900, 721858700, 673652300, 688070200, 637263500, 692825800, 620957100, 607789000]</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.04760000000000002</v>
+        <v>0.0544</v>
       </c>
       <c r="D59" t="n">
         <v>3</v>
@@ -1502,11 +1502,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[640459700, 607799400, 588348500, 668037400, 721707900, 745014700, 710267300, 638613000, 774502400, 818455000]</t>
+          <t>[609169300, 660966800, 613254200, 610941500, 740616500, 723857000, 682591200, 680463400, 718420600, 828807600]</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.05520000000000001</v>
+        <v>0.05480000000000001</v>
       </c>
       <c r="D60" t="n">
         <v>4</v>
@@ -1520,11 +1520,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[625857800, 628054700, 595755200, 659602600, 723476000, 653524000, 740095600, 687914200, 588729700, 603018600]</t>
+          <t>[661301900, 640875700, 698790600, 606645900, 707871300, 661886500, 558836400, 727439300, 873897800, 642777800]</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.03920000000000001</v>
+        <v>0.03000000000000001</v>
       </c>
       <c r="D61" t="n">
         <v>5</v>
